--- a/cyclers/nhr-9200-three-cell-parallel/V0.1.0/NHR-parallel-V0.1.0.xlsx
+++ b/cyclers/nhr-9200-three-cell-parallel/V0.1.0/NHR-parallel-V0.1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Battery-Lab-Hardware\cyclers\nhr-9200-three-cell-parallel\V0.1.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01A482F-2B36-486A-8E76-36951A389F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A74688D9-7FB5-48D6-BD86-D34AB26882FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-150" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -791,7 +791,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -850,53 +850,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1814,1052 +1768,1038 @@
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="22" t="s">
+      <c r="A21" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="29" t="s">
+      <c r="D21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="2">
         <v>2</v>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="9">
         <v>2.72</v>
       </c>
-      <c r="G21" s="34">
+      <c r="G21" s="9">
         <v>5.44</v>
       </c>
-      <c r="H21" s="32"/>
-      <c r="I21" s="28" t="s">
+      <c r="H21" s="5"/>
+      <c r="I21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J21" s="27"/>
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="25" t="s">
+      <c r="A22" s="10" t="s">
         <v>23</v>
       </c>
       <c r="B22" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="29" t="s">
+      <c r="D22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E22" s="29">
-        <v>1</v>
-      </c>
-      <c r="F22" s="34">
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" s="9">
         <v>12.54</v>
       </c>
-      <c r="G22" s="34">
+      <c r="G22" s="9">
         <v>12.54</v>
       </c>
-      <c r="H22" s="32"/>
-      <c r="I22" s="28" t="s">
+      <c r="H22" s="5"/>
+      <c r="I22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J22" s="28" t="s">
+      <c r="J22" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="10" t="s">
         <v>28</v>
       </c>
       <c r="B23" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="29" t="s">
+      <c r="D23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="29">
-        <v>1</v>
-      </c>
-      <c r="F23" s="34">
+      <c r="E23" s="2">
+        <v>1</v>
+      </c>
+      <c r="F23" s="9">
         <v>12.54</v>
       </c>
-      <c r="G23" s="34">
+      <c r="G23" s="9">
         <v>12.54</v>
       </c>
-      <c r="H23" s="32"/>
-      <c r="I23" s="28" t="s">
+      <c r="H23" s="5"/>
+      <c r="I23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J23" s="28" t="s">
+      <c r="J23" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="25" t="s">
+      <c r="A24" s="10" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="29" t="s">
+      <c r="D24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="29">
-        <v>1</v>
-      </c>
-      <c r="F24" s="34">
+      <c r="E24" s="2">
+        <v>1</v>
+      </c>
+      <c r="F24" s="9">
         <v>128.19</v>
       </c>
-      <c r="G24" s="34">
+      <c r="G24" s="9">
         <v>128.19</v>
       </c>
-      <c r="H24" s="32"/>
-      <c r="I24" s="28" t="s">
+      <c r="H24" s="5"/>
+      <c r="I24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J24" s="31"/>
+      <c r="J24" s="4"/>
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="10" t="s">
         <v>78</v>
       </c>
       <c r="B25" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C25" s="38" t="s">
+      <c r="C25" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="D25" s="29" t="s">
+      <c r="D25" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E25" s="29">
-        <v>1</v>
-      </c>
-      <c r="F25" s="34">
+      <c r="E25" s="2">
+        <v>1</v>
+      </c>
+      <c r="F25" s="9">
         <v>6.15</v>
       </c>
-      <c r="G25" s="34">
+      <c r="G25" s="9">
         <v>6.15</v>
       </c>
-      <c r="H25" s="32"/>
-      <c r="I25" s="28" t="s">
+      <c r="H25" s="5"/>
+      <c r="I25" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="J25" s="31"/>
+      <c r="J25" s="4"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="10" t="s">
         <v>79</v>
       </c>
       <c r="B26" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D26" s="29" t="s">
+      <c r="D26" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="2">
         <v>2</v>
       </c>
-      <c r="F26" s="34">
+      <c r="F26" s="9">
         <v>2.4</v>
       </c>
-      <c r="G26" s="34">
+      <c r="G26" s="9">
         <v>4.8</v>
       </c>
-      <c r="H26" s="32"/>
-      <c r="I26" s="28" t="s">
+      <c r="H26" s="5"/>
+      <c r="I26" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="J26" s="31"/>
+      <c r="J26" s="4"/>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="10" t="s">
         <v>80</v>
       </c>
       <c r="B27" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D27" s="29" t="s">
+      <c r="D27" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E27" s="29">
+      <c r="E27" s="2">
         <v>2</v>
       </c>
-      <c r="F27" s="34">
+      <c r="F27" s="9">
         <v>2.4</v>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="9">
         <v>4.8</v>
       </c>
-      <c r="H27" s="32"/>
-      <c r="I27" s="28" t="s">
+      <c r="H27" s="5"/>
+      <c r="I27" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="J27" s="31"/>
+      <c r="J27" s="4"/>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="25" t="s">
+      <c r="A28" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B28" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="31" t="s">
+      <c r="D28" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E28" s="29">
-        <v>1</v>
-      </c>
-      <c r="F28" s="34">
+      <c r="E28" s="2">
+        <v>1</v>
+      </c>
+      <c r="F28" s="9">
         <v>72.62</v>
       </c>
-      <c r="G28" s="34">
+      <c r="G28" s="9">
         <v>72.62</v>
       </c>
-      <c r="H28" s="32"/>
-      <c r="I28" s="28" t="s">
+      <c r="H28" s="5"/>
+      <c r="I28" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J28" s="31"/>
+      <c r="J28" s="4"/>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
+      <c r="A29" t="s">
         <v>81</v>
       </c>
       <c r="B29" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C29" s="27" t="s">
+      <c r="C29" t="s">
         <v>118</v>
       </c>
-      <c r="D29" s="27" t="s">
+      <c r="D29" t="s">
         <v>119</v>
       </c>
-      <c r="E29" s="27">
-        <v>1</v>
-      </c>
-      <c r="F29" s="41">
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29" s="23">
         <v>5.14</v>
       </c>
-      <c r="G29" s="41">
+      <c r="G29" s="23">
         <v>5.14</v>
       </c>
-      <c r="H29" s="27" t="s">
+      <c r="H29" t="s">
         <v>120</v>
       </c>
-      <c r="I29" s="27" t="s">
+      <c r="I29" t="s">
         <v>121</v>
       </c>
-      <c r="J29" s="31"/>
+      <c r="J29" s="4"/>
     </row>
     <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="25" t="s">
+      <c r="A30" s="10" t="s">
         <v>82</v>
       </c>
       <c r="B30" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D30" s="29" t="s">
+      <c r="D30" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E30" s="29">
-        <v>1</v>
-      </c>
-      <c r="F30" s="33">
+      <c r="E30" s="2">
+        <v>1</v>
+      </c>
+      <c r="F30" s="8">
         <v>2.72</v>
       </c>
-      <c r="G30" s="34">
+      <c r="G30" s="9">
         <v>2.72</v>
       </c>
-      <c r="H30" s="32"/>
-      <c r="I30" s="30" t="s">
+      <c r="H30" s="5"/>
+      <c r="I30" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="J30" s="31"/>
+      <c r="J30" s="4"/>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="10" t="s">
         <v>83</v>
       </c>
       <c r="B31" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D31" s="29" t="s">
+      <c r="D31" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E31" s="29">
+      <c r="E31" s="2">
         <v>4</v>
       </c>
-      <c r="F31" s="33">
+      <c r="F31" s="8">
         <v>0.37</v>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="9">
         <v>1.48</v>
       </c>
-      <c r="H31" s="32"/>
-      <c r="I31" s="30" t="s">
+      <c r="H31" s="5"/>
+      <c r="I31" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="J31" s="31"/>
+      <c r="J31" s="4"/>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="26" t="s">
+      <c r="A32" s="22" t="s">
         <v>84</v>
       </c>
       <c r="B32" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C32" s="35" t="s">
+      <c r="C32" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="D32" s="35" t="s">
+      <c r="D32" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="E32" s="36">
+      <c r="E32" s="12">
         <v>4</v>
       </c>
-      <c r="F32" s="37">
+      <c r="F32" s="13">
         <v>0.04</v>
       </c>
-      <c r="G32" s="34">
+      <c r="G32" s="9">
         <v>0.16</v>
       </c>
-      <c r="H32" s="35"/>
-      <c r="I32" s="40" t="s">
+      <c r="H32" s="11"/>
+      <c r="I32" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="J32" s="31"/>
+      <c r="J32" s="4"/>
     </row>
     <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="24" t="s">
+      <c r="A33" s="4" t="s">
         <v>85</v>
       </c>
       <c r="B33" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C33" s="31" t="s">
+      <c r="C33" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D33" s="31" t="s">
+      <c r="D33" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E33" s="31">
-        <v>1</v>
-      </c>
-      <c r="F33" s="42">
+      <c r="E33" s="4">
+        <v>1</v>
+      </c>
+      <c r="F33" s="24">
         <v>9.99</v>
       </c>
-      <c r="G33" s="34">
+      <c r="G33" s="9">
         <v>9.99</v>
       </c>
-      <c r="H33" s="35"/>
-      <c r="I33" s="43" t="s">
+      <c r="H33" s="11"/>
+      <c r="I33" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="J33" s="31"/>
+      <c r="J33" s="4"/>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="4" t="s">
         <v>86</v>
       </c>
       <c r="B34" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="31" t="s">
+      <c r="C34" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D34" s="31" t="s">
+      <c r="D34" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="E34" s="31">
+      <c r="E34" s="4">
         <v>2</v>
       </c>
-      <c r="F34" s="42">
+      <c r="F34" s="24">
         <v>11.18</v>
       </c>
-      <c r="G34" s="34">
+      <c r="G34" s="9">
         <v>22.36</v>
       </c>
-      <c r="H34" s="35"/>
-      <c r="I34" s="43" t="s">
+      <c r="H34" s="11"/>
+      <c r="I34" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="J34" s="31"/>
+      <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="24" t="s">
+      <c r="A35" s="4" t="s">
         <v>87</v>
       </c>
       <c r="B35" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="31" t="s">
+      <c r="C35" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D35" s="31" t="s">
+      <c r="D35" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="E35" s="31">
+      <c r="E35" s="4">
         <v>6</v>
       </c>
-      <c r="F35" s="42">
+      <c r="F35" s="24">
         <v>3.85</v>
       </c>
-      <c r="G35" s="34">
+      <c r="G35" s="9">
         <v>23.1</v>
       </c>
-      <c r="H35" s="35"/>
-      <c r="I35" s="43" t="s">
+      <c r="H35" s="11"/>
+      <c r="I35" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="J35" s="31"/>
+      <c r="J35" s="4"/>
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+      <c r="A36" s="4" t="s">
         <v>88</v>
       </c>
       <c r="B36" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C36" s="31" t="s">
+      <c r="C36" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D36" s="31" t="s">
+      <c r="D36" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="E36" s="31">
+      <c r="E36" s="4">
         <v>2</v>
       </c>
-      <c r="F36" s="42">
+      <c r="F36" s="24">
         <v>8.19</v>
       </c>
-      <c r="G36" s="34">
+      <c r="G36" s="9">
         <v>16.38</v>
       </c>
-      <c r="H36" s="35"/>
-      <c r="I36" s="43" t="s">
+      <c r="H36" s="11"/>
+      <c r="I36" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="J36" s="31"/>
+      <c r="J36" s="4"/>
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="24" t="s">
+      <c r="A37" s="4" t="s">
         <v>89</v>
       </c>
       <c r="B37" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C37" s="31" t="s">
+      <c r="C37" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D37" s="31" t="s">
+      <c r="D37" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="E37" s="31">
-        <v>1</v>
-      </c>
-      <c r="F37" s="42">
+      <c r="E37" s="4">
+        <v>1</v>
+      </c>
+      <c r="F37" s="24">
         <v>15.98</v>
       </c>
-      <c r="G37" s="34">
+      <c r="G37" s="9">
         <v>15.98</v>
       </c>
-      <c r="H37" s="35"/>
-      <c r="I37" s="43" t="s">
+      <c r="H37" s="11"/>
+      <c r="I37" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="J37" s="31"/>
+      <c r="J37" s="4"/>
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+      <c r="A38" s="4" t="s">
         <v>90</v>
       </c>
       <c r="B38" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C38" s="31" t="s">
+      <c r="C38" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D38" s="31" t="s">
+      <c r="D38" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="E38" s="31">
-        <v>1</v>
-      </c>
-      <c r="F38" s="42">
+      <c r="E38" s="4">
+        <v>1</v>
+      </c>
+      <c r="F38" s="24">
         <v>19.989999999999998</v>
       </c>
-      <c r="G38" s="34">
+      <c r="G38" s="9">
         <v>19.989999999999998</v>
       </c>
-      <c r="H38" s="35"/>
-      <c r="I38" s="43" t="s">
+      <c r="H38" s="11"/>
+      <c r="I38" s="25" t="s">
         <v>148</v>
       </c>
-      <c r="J38" s="31"/>
+      <c r="J38" s="4"/>
     </row>
     <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="26" t="s">
+      <c r="A39" s="22" t="s">
         <v>91</v>
       </c>
       <c r="B39" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C39" s="35" t="s">
+      <c r="C39" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="D39" s="35" t="s">
+      <c r="D39" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="E39" s="36">
-        <v>1</v>
-      </c>
-      <c r="F39" s="37">
+      <c r="E39" s="12">
+        <v>1</v>
+      </c>
+      <c r="F39" s="13">
         <v>820</v>
       </c>
-      <c r="G39" s="34">
+      <c r="G39" s="9">
         <v>820</v>
       </c>
-      <c r="H39" s="34" t="s">
+      <c r="H39" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="I39" s="35" t="s">
+      <c r="I39" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="J39" s="31"/>
+      <c r="J39" s="4"/>
     </row>
     <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="26" t="s">
+      <c r="A40" s="22" t="s">
         <v>92</v>
       </c>
       <c r="B40" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C40" s="35" t="s">
+      <c r="C40" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="D40" s="35" t="s">
+      <c r="D40" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="E40" s="36">
+      <c r="E40" s="12">
         <v>3</v>
       </c>
-      <c r="F40" s="37">
+      <c r="F40" s="13">
         <v>235</v>
       </c>
-      <c r="G40" s="34">
+      <c r="G40" s="9">
         <v>705</v>
       </c>
-      <c r="H40" s="34" t="s">
+      <c r="H40" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I40" s="35" t="s">
+      <c r="I40" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="J40" s="31"/>
+      <c r="J40" s="4"/>
     </row>
     <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="26" t="s">
+      <c r="A41" s="22" t="s">
         <v>93</v>
       </c>
       <c r="B41" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="35" t="s">
+      <c r="C41" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D41" s="35" t="s">
+      <c r="D41" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E41" s="36">
+      <c r="E41" s="12">
         <v>3</v>
       </c>
-      <c r="F41" s="37">
+      <c r="F41" s="13">
         <v>135.47</v>
       </c>
-      <c r="G41" s="34">
+      <c r="G41" s="9">
         <v>406.40999999999997</v>
       </c>
-      <c r="H41" s="34" t="s">
+      <c r="H41" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="I41" s="35" t="s">
+      <c r="I41" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="J41" s="31"/>
+      <c r="J41" s="4"/>
     </row>
     <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="26" t="s">
+      <c r="A42" s="22" t="s">
         <v>94</v>
       </c>
       <c r="B42" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="35" t="s">
+      <c r="C42" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="D42" s="39" t="s">
+      <c r="D42" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="E42" s="36">
-        <v>1</v>
-      </c>
-      <c r="F42" s="37">
+      <c r="E42" s="12">
+        <v>1</v>
+      </c>
+      <c r="F42" s="13">
         <v>3048</v>
       </c>
-      <c r="G42" s="34">
+      <c r="G42" s="9">
         <v>3048</v>
       </c>
-      <c r="H42" s="27"/>
-      <c r="I42" s="40" t="s">
+      <c r="I42" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="J42" s="40" t="s">
+      <c r="J42" s="21" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="23" t="s">
+      <c r="A43" s="2" t="s">
         <v>95</v>
       </c>
       <c r="B43" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C43" s="35" t="s">
+      <c r="C43" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="D43" s="29" t="s">
+      <c r="D43" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E43" s="29">
-        <v>1</v>
-      </c>
-      <c r="F43" s="32">
+      <c r="E43" s="2">
+        <v>1</v>
+      </c>
+      <c r="F43" s="5">
         <v>162.72</v>
       </c>
-      <c r="G43" s="34">
+      <c r="G43" s="9">
         <v>162.72</v>
       </c>
-      <c r="H43" s="32"/>
-      <c r="I43" s="30" t="s">
+      <c r="H43" s="5"/>
+      <c r="I43" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="J43" s="30" t="s">
+      <c r="J43" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="26" t="s">
+      <c r="A44" s="22" t="s">
         <v>96</v>
       </c>
       <c r="B44" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C44" s="35" t="s">
+      <c r="C44" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="D44" s="35" t="s">
+      <c r="D44" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="E44" s="35">
-        <v>1</v>
-      </c>
-      <c r="F44" s="36">
+      <c r="E44" s="11">
+        <v>1</v>
+      </c>
+      <c r="F44" s="12">
         <v>162.72</v>
       </c>
-      <c r="G44" s="34">
+      <c r="G44" s="9">
         <v>162.72</v>
       </c>
-      <c r="H44" s="27"/>
-      <c r="I44" s="35" t="s">
+      <c r="I44" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="J44" s="40" t="s">
+      <c r="J44" s="21" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="23" t="s">
+      <c r="A45" s="2" t="s">
         <v>97</v>
       </c>
       <c r="B45" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="29" t="s">
+      <c r="C45" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D45" s="29"/>
-      <c r="E45" s="29">
-        <v>1</v>
-      </c>
-      <c r="F45" s="32">
+      <c r="D45" s="2"/>
+      <c r="E45" s="2">
+        <v>1</v>
+      </c>
+      <c r="F45" s="5">
         <v>22.56</v>
       </c>
-      <c r="G45" s="34">
+      <c r="G45" s="9">
         <v>22.56</v>
       </c>
-      <c r="H45" s="27"/>
-      <c r="I45" s="30" t="s">
+      <c r="I45" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="J45" s="40"/>
+      <c r="J45" s="21"/>
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="22" t="s">
+      <c r="A46" t="s">
         <v>98</v>
       </c>
       <c r="B46" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C46" s="27" t="s">
+      <c r="C46" t="s">
         <v>173</v>
       </c>
-      <c r="D46" s="27" t="s">
+      <c r="D46" t="s">
         <v>174</v>
       </c>
-      <c r="E46" s="27">
-        <v>1</v>
-      </c>
-      <c r="F46" s="41">
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="F46" s="23">
         <v>88.78</v>
       </c>
-      <c r="G46" s="34">
+      <c r="G46" s="9">
         <v>88.78</v>
       </c>
-      <c r="H46" s="27" t="s">
+      <c r="H46" t="s">
         <v>175</v>
       </c>
-      <c r="I46" s="27" t="s">
+      <c r="I46" t="s">
         <v>176</v>
       </c>
-      <c r="J46" s="27"/>
     </row>
     <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="22" t="s">
+      <c r="A47" t="s">
         <v>99</v>
       </c>
       <c r="B47" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C47" s="27" t="s">
+      <c r="C47" t="s">
         <v>177</v>
       </c>
-      <c r="D47" s="27" t="s">
+      <c r="D47" t="s">
         <v>178</v>
       </c>
-      <c r="E47" s="27">
-        <v>1</v>
-      </c>
-      <c r="F47" s="41">
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47" s="23">
         <v>357.1</v>
       </c>
-      <c r="G47" s="34">
+      <c r="G47" s="9">
         <v>357.1</v>
       </c>
-      <c r="H47" s="27" t="s">
+      <c r="H47" t="s">
         <v>179</v>
       </c>
-      <c r="I47" s="27" t="s">
+      <c r="I47" t="s">
         <v>180</v>
       </c>
-      <c r="J47" s="27"/>
     </row>
     <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="22" t="s">
+      <c r="A48" t="s">
         <v>100</v>
       </c>
       <c r="B48" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="27" t="s">
+      <c r="C48" t="s">
         <v>181</v>
       </c>
-      <c r="D48" s="27" t="s">
+      <c r="D48" t="s">
         <v>182</v>
       </c>
-      <c r="E48" s="27">
+      <c r="E48">
         <v>3</v>
       </c>
-      <c r="F48" s="41">
+      <c r="F48" s="23">
         <v>106.72</v>
       </c>
-      <c r="G48" s="34">
+      <c r="G48" s="9">
         <v>320.15999999999997</v>
       </c>
-      <c r="H48" s="27" t="s">
+      <c r="H48" t="s">
         <v>183</v>
       </c>
-      <c r="I48" s="27" t="s">
+      <c r="I48" t="s">
         <v>184</v>
       </c>
-      <c r="J48" s="27"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="22" t="s">
+      <c r="A49" t="s">
         <v>101</v>
       </c>
       <c r="B49" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C49" s="27" t="s">
+      <c r="C49" t="s">
         <v>185</v>
       </c>
-      <c r="D49" s="27" t="s">
+      <c r="D49" t="s">
         <v>186</v>
       </c>
-      <c r="E49" s="27">
-        <v>1</v>
-      </c>
-      <c r="F49" s="41">
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="F49" s="23">
         <v>137.65</v>
       </c>
-      <c r="G49" s="34">
+      <c r="G49" s="9">
         <v>137.65</v>
       </c>
-      <c r="H49" s="27" t="s">
+      <c r="H49" t="s">
         <v>187</v>
       </c>
-      <c r="I49" s="27" t="s">
+      <c r="I49" t="s">
         <v>188</v>
       </c>
-      <c r="J49" s="27"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="22" t="s">
+      <c r="A50" t="s">
         <v>102</v>
       </c>
       <c r="B50" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C50" s="27" t="s">
+      <c r="C50" t="s">
         <v>189</v>
       </c>
-      <c r="D50" s="27" t="s">
+      <c r="D50" t="s">
         <v>190</v>
       </c>
-      <c r="E50" s="27">
-        <v>1</v>
-      </c>
-      <c r="F50" s="41">
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50" s="23">
         <v>56.85</v>
       </c>
-      <c r="G50" s="34">
+      <c r="G50" s="9">
         <v>56.85</v>
       </c>
-      <c r="H50" s="27" t="s">
+      <c r="H50" t="s">
         <v>191</v>
       </c>
-      <c r="I50" s="27" t="s">
+      <c r="I50" t="s">
         <v>192</v>
       </c>
-      <c r="J50" s="27"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="22" t="s">
+      <c r="A51" t="s">
         <v>103</v>
       </c>
       <c r="B51" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C51" s="27" t="s">
+      <c r="C51" t="s">
         <v>193</v>
       </c>
-      <c r="D51" s="27" t="s">
+      <c r="D51" t="s">
         <v>194</v>
       </c>
-      <c r="E51" s="27">
-        <v>1</v>
-      </c>
-      <c r="F51" s="41">
+      <c r="E51">
+        <v>1</v>
+      </c>
+      <c r="F51" s="23">
         <v>281.25</v>
       </c>
-      <c r="G51" s="34">
+      <c r="G51" s="9">
         <v>281.25</v>
       </c>
-      <c r="H51" s="27" t="s">
+      <c r="H51" t="s">
         <v>195</v>
       </c>
-      <c r="I51" s="27" t="s">
+      <c r="I51" t="s">
         <v>196</v>
       </c>
-      <c r="J51" s="27"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="22" t="s">
+      <c r="A52" t="s">
         <v>104</v>
       </c>
       <c r="B52" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C52" s="27" t="s">
+      <c r="C52" t="s">
         <v>197</v>
       </c>
-      <c r="D52" s="27" t="s">
+      <c r="D52" t="s">
         <v>198</v>
       </c>
-      <c r="E52" s="27">
+      <c r="E52">
         <v>3</v>
       </c>
-      <c r="F52" s="41">
+      <c r="F52" s="23">
         <v>1.71</v>
       </c>
-      <c r="G52" s="34">
+      <c r="G52" s="9">
         <v>5.13</v>
       </c>
-      <c r="H52" s="27"/>
-      <c r="I52" s="41" t="s">
+      <c r="I52" s="23" t="s">
         <v>199</v>
       </c>
-      <c r="J52" s="27" t="s">
+      <c r="J52" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="22" t="s">
+      <c r="A53" t="s">
         <v>105</v>
       </c>
       <c r="B53" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="27" t="s">
+      <c r="C53" t="s">
         <v>201</v>
       </c>
-      <c r="D53" s="27" t="s">
+      <c r="D53" t="s">
         <v>202</v>
       </c>
-      <c r="E53" s="27">
-        <v>1</v>
-      </c>
-      <c r="F53" s="33">
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="F53" s="8">
         <v>765</v>
       </c>
-      <c r="G53" s="34">
+      <c r="G53" s="9">
         <v>765</v>
       </c>
-      <c r="H53" s="33" t="s">
+      <c r="H53" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="I53" s="27" t="s">
+      <c r="I53" t="s">
         <v>204</v>
       </c>
-      <c r="J53" s="28" t="s">
+      <c r="J53" s="1" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="22" t="s">
+      <c r="A54" t="s">
         <v>106</v>
       </c>
       <c r="B54" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C54" s="27" t="s">
+      <c r="C54" t="s">
         <v>206</v>
       </c>
-      <c r="D54" s="27" t="s">
+      <c r="D54" t="s">
         <v>207</v>
       </c>
-      <c r="E54" s="27">
-        <v>1</v>
-      </c>
-      <c r="F54" s="33">
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54" s="8">
         <v>1027.1199999999999</v>
       </c>
-      <c r="G54" s="34">
+      <c r="G54" s="9">
         <v>1027.1199999999999</v>
       </c>
-      <c r="H54" s="33" t="s">
+      <c r="H54" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="I54" s="27" t="s">
+      <c r="I54" t="s">
         <v>209</v>
       </c>
-      <c r="J54" s="28" t="s">
+      <c r="J54" s="1" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="22" t="s">
+      <c r="A55" t="s">
         <v>107</v>
       </c>
       <c r="B55" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C55" s="27" t="s">
+      <c r="C55" t="s">
         <v>211</v>
       </c>
-      <c r="D55" s="27" t="s">
+      <c r="D55" t="s">
         <v>212</v>
       </c>
-      <c r="E55" s="27">
-        <v>1</v>
-      </c>
-      <c r="F55" s="41">
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55" s="23">
         <v>7877</v>
       </c>
-      <c r="G55" s="27"/>
-      <c r="H55" s="27" t="s">
+      <c r="H55" t="s">
         <v>213</v>
       </c>
-      <c r="I55" s="27" t="s">
+      <c r="I55" t="s">
         <v>214</v>
       </c>
-      <c r="J55" s="27"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="22" t="s">
+      <c r="A56" t="s">
         <v>108</v>
       </c>
       <c r="B56" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C56" s="27" t="s">
+      <c r="C56" t="s">
         <v>215</v>
       </c>
-      <c r="D56" s="27" t="s">
+      <c r="D56" t="s">
         <v>216</v>
       </c>
-      <c r="E56" s="27">
-        <v>1</v>
-      </c>
-      <c r="F56" s="41">
+      <c r="E56">
+        <v>1</v>
+      </c>
+      <c r="F56" s="23">
         <v>31.99</v>
       </c>
-      <c r="G56" s="41">
+      <c r="G56" s="23">
         <v>31.99</v>
       </c>
-      <c r="H56" s="27" t="s">
+      <c r="H56" t="s">
         <v>217</v>
       </c>
-      <c r="I56" s="27" t="s">
+      <c r="I56" t="s">
         <v>218</v>
       </c>
-      <c r="J56" s="27"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B57" s="17"/>
@@ -2928,8 +2868,10 @@
     <hyperlink ref="J53" r:id="rId41" xr:uid="{8049C48E-C4B0-495E-9124-9CCD92510653}"/>
     <hyperlink ref="J54" r:id="rId42" xr:uid="{20B5B22B-708C-4B8C-AA8D-54CE2BC9E7C0}"/>
     <hyperlink ref="J44" r:id="rId43" xr:uid="{CA934B0B-0450-4ADA-AF73-0EF6C2AA1AC8}"/>
+    <hyperlink ref="I40" r:id="rId44" xr:uid="{87DA6062-3B84-4BEC-9C2A-3105CB068282}"/>
+    <hyperlink ref="I39" r:id="rId45" xr:uid="{247862D9-AA8E-42DE-8A47-9D24CF605D75}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId44"/>
+  <pageSetup orientation="portrait" r:id="rId46"/>
 </worksheet>
 </file>